--- a/specs/Wiring_6/Wiring_6_spec.xlsx
+++ b/specs/Wiring_6/Wiring_6_spec.xlsx
@@ -515,7 +515,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>?</t>
+          <t>Volkswagen</t>
         </is>
       </c>
     </row>
@@ -527,7 +527,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>не указана</t>
+          <t>Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
     </row>
@@ -658,7 +658,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -717,7 +717,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -833,7 +833,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -890,7 +890,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1004,7 +1004,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1063,7 +1063,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1122,7 +1122,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -1504,7 +1504,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -1558,7 +1558,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1720,7 +1720,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1938,7 +1938,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -2046,7 +2046,7 @@
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2100,7 +2100,7 @@
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2154,7 +2154,7 @@
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C16" s="2" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -2322,7 +2322,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
@@ -2438,7 +2438,7 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C21" s="2" t="inlineStr">
@@ -2494,7 +2494,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C22" s="3" t="inlineStr">
@@ -2552,7 +2552,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C23" s="3" t="inlineStr">
@@ -2610,7 +2610,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C24" s="3" t="inlineStr">
@@ -2668,7 +2668,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C25" s="3" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C26" s="2" t="inlineStr">
@@ -2782,7 +2782,7 @@
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C27" s="3" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C28" s="3" t="inlineStr">
@@ -2898,7 +2898,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C29" s="3" t="inlineStr">
@@ -2956,7 +2956,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C30" s="3" t="inlineStr">
@@ -3014,7 +3014,7 @@
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
@@ -3070,7 +3070,7 @@
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
@@ -3124,7 +3124,7 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
@@ -3178,7 +3178,7 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
@@ -3232,7 +3232,7 @@
       </c>
       <c r="B35" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C35" s="2" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="B36" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C36" s="2" t="inlineStr">
@@ -3340,7 +3340,7 @@
       </c>
       <c r="B37" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C37" s="2" t="inlineStr">
@@ -3394,7 +3394,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C38" s="3" t="inlineStr">
@@ -3452,7 +3452,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C39" s="3" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
@@ -3618,7 +3618,7 @@
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C42" s="3" t="inlineStr">
@@ -3676,7 +3676,7 @@
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C43" s="3" t="inlineStr">
@@ -3734,7 +3734,7 @@
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C44" s="2" t="inlineStr">
@@ -3788,7 +3788,7 @@
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
@@ -3842,7 +3842,7 @@
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
@@ -3896,7 +3896,7 @@
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C50" s="2" t="inlineStr">
@@ -4116,7 +4116,7 @@
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C51" s="2" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
@@ -4340,7 +4340,7 @@
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4535,7 +4535,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -4627,7 +4627,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4673,7 +4673,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -4765,7 +4765,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
@@ -4903,7 +4903,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4949,7 +4949,7 @@
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4995,7 +4995,7 @@
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
@@ -5041,7 +5041,7 @@
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>модель не указана</t>
+          <t>Volkswagen Polo V SD 2010-2020 (1)</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">

--- a/specs/Wiring_6/Wiring_6_spec.xlsx
+++ b/specs/Wiring_6/Wiring_6_spec.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Разъёмы'!$A$1:$M$12</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Распиновка'!$A$1:$N$56</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'BOM'!$A$1:$J$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Замечания'!$A$1:$D$18</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Замечания'!$A$1:$D$19</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Каталог'!$A$1:$H$13</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5093,7 +5093,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D18"/>
+  <dimension ref="A1:D19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -5327,7 +5327,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Гнездо FASTON 41450-1 рассчитано на 2.08–5.26 мм², а провод на листах 2-2…2-4, 3-2…3-4, 6-2 — 1 мм². Обжим будет ненадёжным.</t>
+          <t>Гнездо FASTON 41450-1 рассчитано на 2.08–5.26 мм², а провод на листах 2-2…2-4, 3-2…3-4, 6-2, 10-2…10-4 — 1 мм². Обжим будет ненадёжным.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -5416,8 +5416,28 @@
         </is>
       </c>
     </row>
+    <row r="19">
+      <c r="A19" s="2" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Контакты не указаны в BOM</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Для части разъёмов (Yazaki, VAG, Molex NSCC, колодки ВАЗ) контакты в BOM не указаны или указаны без номера.</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Подобрать по каталогу производителя корпуса под 0.5–1.0 мм².</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:D18"/>
+  <autoFilter ref="A1:D19"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
